--- a/results/dml_ate_HTE_manager_efficacy_index.xlsx
+++ b/results/dml_ate_HTE_manager_efficacy_index.xlsx
@@ -477,10 +477,10 @@
         <v>0.3814097435289842</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2161633346665066</v>
+        <v>0.2161633346665067</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.04227039241736891</v>
+        <v>-0.04227039241736896</v>
       </c>
       <c r="E2" t="n">
         <v>0.8050898794753372</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(-0.04227039241736891, 0.8050898794753372)</t>
+          <t>(-0.04227039241736896, 0.8050898794753372)</t>
         </is>
       </c>
     </row>

--- a/results/dml_ate_HTE_manager_efficacy_index.xlsx
+++ b/results/dml_ate_HTE_manager_efficacy_index.xlsx
@@ -477,13 +477,13 @@
         <v>0.3433500649575789</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1972059345704637</v>
+        <v>0.1972059345704636</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.04317356680052992</v>
+        <v>-0.04317356680052986</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7298736967156877</v>
+        <v>0.7298736967156876</v>
       </c>
       <c r="F2" t="n">
         <v>0.1266840836012862</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(-0.04317356680052992, 0.7298736967156877)</t>
+          <t>(-0.04317356680052986, 0.7298736967156876)</t>
         </is>
       </c>
     </row>

--- a/results/dml_ate_HTE_manager_efficacy_index.xlsx
+++ b/results/dml_ate_HTE_manager_efficacy_index.xlsx
@@ -474,16 +474,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.343350064957579</v>
+        <v>0.3433500649575789</v>
       </c>
       <c r="C2" t="n">
         <v>0.1972059345704637</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.04317356680052986</v>
+        <v>-0.04317356680052981</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7298736967156878</v>
+        <v>0.7298736967156877</v>
       </c>
       <c r="F2" t="n">
         <v>0.1266840836012862</v>
@@ -746,11 +746,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.343350064957579</v>
+        <v>0.3433500649575789</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(-0.04317356680052986, 0.7298736967156878)</t>
+          <t>(-0.043173566800529806, 0.7298736967156877)</t>
         </is>
       </c>
     </row>

--- a/results/dml_ate_HTE_manager_efficacy_index.xlsx
+++ b/results/dml_ate_HTE_manager_efficacy_index.xlsx
@@ -480,7 +480,7 @@
         <v>0.1915944011631294</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005185661878034153</v>
+        <v>0.005185661878034098</v>
       </c>
       <c r="E2" t="n">
         <v>0.7562357144375014</v>
@@ -700,7 +700,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(0.0051856618780341535, 0.7562357144375014)</t>
+          <t>(0.005185661878034098, 0.7562357144375014)</t>
         </is>
       </c>
     </row>
